--- a/artfynd/A 4450-2025 artfynd.xlsx
+++ b/artfynd/A 4450-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124572169</v>
+        <v>124571954</v>
       </c>
       <c r="B2" t="n">
-        <v>56722</v>
+        <v>57666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,14 +714,10 @@
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>övernattning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -731,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>735753</v>
+        <v>735788</v>
       </c>
       <c r="R2" t="n">
-        <v>7094155</v>
+        <v>7094109</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,17 +757,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -798,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124571954</v>
+        <v>124572176</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>56722</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,25 +801,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -837,10 +828,14 @@
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>övernattning</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -850,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>735788</v>
+        <v>735831</v>
       </c>
       <c r="R3" t="n">
-        <v>7094109</v>
+        <v>7094139</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,12 +875,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,7 +912,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124571918</v>
+        <v>124571916</v>
       </c>
       <c r="B4" t="n">
         <v>56722</v>
@@ -960,10 +960,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>735703</v>
+        <v>735671</v>
       </c>
       <c r="R4" t="n">
-        <v>7094102</v>
+        <v>7094195</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1022,7 +1022,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124571976</v>
+        <v>124572068</v>
       </c>
       <c r="B5" t="n">
         <v>56722</v>
@@ -1070,10 +1070,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>735843</v>
+        <v>735946</v>
       </c>
       <c r="R5" t="n">
-        <v>7093984</v>
+        <v>7094100</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1132,7 +1132,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124572048</v>
+        <v>124571964</v>
       </c>
       <c r="B6" t="n">
         <v>56722</v>
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>735905</v>
+        <v>735877</v>
       </c>
       <c r="R6" t="n">
-        <v>7094143</v>
+        <v>7094173</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1242,7 +1242,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124572161</v>
+        <v>124572088</v>
       </c>
       <c r="B7" t="n">
         <v>56722</v>
@@ -1275,20 +1275,12 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>övernattning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1298,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>735754</v>
+        <v>735949</v>
       </c>
       <c r="R7" t="n">
-        <v>7094207</v>
+        <v>7094084</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1328,17 +1320,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,7 +1352,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124571964</v>
+        <v>124571938</v>
       </c>
       <c r="B8" t="n">
         <v>56722</v>
@@ -1413,10 +1400,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>735877</v>
+        <v>735748</v>
       </c>
       <c r="R8" t="n">
-        <v>7094173</v>
+        <v>7094125</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1475,10 +1462,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124572050</v>
+        <v>124571960</v>
       </c>
       <c r="B9" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1487,25 +1474,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1513,7 +1500,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1523,10 +1510,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>735918</v>
+        <v>735822</v>
       </c>
       <c r="R9" t="n">
-        <v>7094133</v>
+        <v>7094149</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1585,7 +1572,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124571938</v>
+        <v>124572008</v>
       </c>
       <c r="B10" t="n">
         <v>56722</v>
@@ -1633,10 +1620,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>735748</v>
+        <v>735894</v>
       </c>
       <c r="R10" t="n">
-        <v>7094125</v>
+        <v>7093968</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1695,7 +1682,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124571973</v>
+        <v>124572169</v>
       </c>
       <c r="B11" t="n">
         <v>56722</v>
@@ -1728,12 +1715,20 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>övernattning</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1743,10 +1738,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>735833</v>
+        <v>735753</v>
       </c>
       <c r="R11" t="n">
-        <v>7094015</v>
+        <v>7094155</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1773,12 +1768,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,7 +1805,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124572068</v>
+        <v>124571973</v>
       </c>
       <c r="B12" t="n">
         <v>56722</v>
@@ -1853,10 +1853,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>735946</v>
+        <v>735833</v>
       </c>
       <c r="R12" t="n">
-        <v>7094100</v>
+        <v>7094015</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1915,7 +1915,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124572066</v>
+        <v>124571918</v>
       </c>
       <c r="B13" t="n">
         <v>56722</v>
@@ -1963,10 +1963,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>735937</v>
+        <v>735703</v>
       </c>
       <c r="R13" t="n">
-        <v>7094116</v>
+        <v>7094102</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1999,11 +1999,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ett av flera natträd med nattspillning och blidntarmstömning under. Dessutom kortspillning under detta. Indikerar spelplats i lämplig biotop för spel.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2030,7 +2025,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124571916</v>
+        <v>124572048</v>
       </c>
       <c r="B14" t="n">
         <v>56722</v>
@@ -2078,10 +2073,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>735671</v>
+        <v>735905</v>
       </c>
       <c r="R14" t="n">
-        <v>7094195</v>
+        <v>7094143</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2140,7 +2135,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124572008</v>
+        <v>124571896</v>
       </c>
       <c r="B15" t="n">
         <v>56722</v>
@@ -2188,10 +2183,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>735894</v>
+        <v>735546</v>
       </c>
       <c r="R15" t="n">
-        <v>7093968</v>
+        <v>7094241</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2224,6 +2219,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Natträd med blindtarmstömning under.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2250,10 +2250,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124571960</v>
+        <v>124572161</v>
       </c>
       <c r="B16" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2262,33 +2262,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>övernattning</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2298,10 +2306,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>735822</v>
+        <v>735754</v>
       </c>
       <c r="R16" t="n">
-        <v>7094149</v>
+        <v>7094207</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2328,12 +2336,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2360,7 +2373,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124572176</v>
+        <v>124572066</v>
       </c>
       <c r="B17" t="n">
         <v>56722</v>
@@ -2393,20 +2406,12 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>övernattning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2416,10 +2421,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>735831</v>
+        <v>735937</v>
       </c>
       <c r="R17" t="n">
-        <v>7094139</v>
+        <v>7094116</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2446,17 +2451,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
+          <t>Ett av flera natträd med nattspillning och blidntarmstömning under. Dessutom kortspillning under detta. Indikerar spelplats i lämplig biotop för spel.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2483,7 +2488,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124571896</v>
+        <v>124571976</v>
       </c>
       <c r="B18" t="n">
         <v>56722</v>
@@ -2531,10 +2536,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>735546</v>
+        <v>735843</v>
       </c>
       <c r="R18" t="n">
-        <v>7094241</v>
+        <v>7093984</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2567,11 +2572,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Natträd med blindtarmstömning under.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2598,7 +2598,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124572088</v>
+        <v>124572050</v>
       </c>
       <c r="B19" t="n">
         <v>56722</v>
@@ -2646,10 +2646,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>735949</v>
+        <v>735918</v>
       </c>
       <c r="R19" t="n">
-        <v>7094084</v>
+        <v>7094133</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 4450-2025 artfynd.xlsx
+++ b/artfynd/A 4450-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124571954</v>
+        <v>124571896</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
+        <v>56722</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,37 +687,33 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>735788</v>
+        <v>735546</v>
       </c>
       <c r="R2" t="n">
-        <v>7094109</v>
+        <v>7094241</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -763,6 +759,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Natträd med blindtarmstömning under.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,7 +790,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124572176</v>
+        <v>124571938</v>
       </c>
       <c r="B3" t="n">
         <v>56722</v>
@@ -822,20 +823,12 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>övernattning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -845,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>735831</v>
+        <v>735748</v>
       </c>
       <c r="R3" t="n">
-        <v>7094139</v>
+        <v>7094125</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,17 +868,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,7 +900,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124571916</v>
+        <v>124572066</v>
       </c>
       <c r="B4" t="n">
         <v>56722</v>
@@ -960,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>735671</v>
+        <v>735937</v>
       </c>
       <c r="R4" t="n">
-        <v>7094195</v>
+        <v>7094116</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,6 +984,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ett av flera natträd med nattspillning och blidntarmstömning under. Dessutom kortspillning under detta. Indikerar spelplats i lämplig biotop för spel.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,7 +1015,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124572068</v>
+        <v>124571973</v>
       </c>
       <c r="B5" t="n">
         <v>56722</v>
@@ -1070,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>735946</v>
+        <v>735833</v>
       </c>
       <c r="R5" t="n">
-        <v>7094100</v>
+        <v>7094015</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1132,7 +1125,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124571964</v>
+        <v>124572008</v>
       </c>
       <c r="B6" t="n">
         <v>56722</v>
@@ -1180,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>735877</v>
+        <v>735894</v>
       </c>
       <c r="R6" t="n">
-        <v>7094173</v>
+        <v>7093968</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1242,7 +1235,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124572088</v>
+        <v>124572068</v>
       </c>
       <c r="B7" t="n">
         <v>56722</v>
@@ -1290,10 +1283,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>735949</v>
+        <v>735946</v>
       </c>
       <c r="R7" t="n">
-        <v>7094084</v>
+        <v>7094100</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1352,7 +1345,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124571938</v>
+        <v>124572088</v>
       </c>
       <c r="B8" t="n">
         <v>56722</v>
@@ -1400,10 +1393,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>735748</v>
+        <v>735949</v>
       </c>
       <c r="R8" t="n">
-        <v>7094125</v>
+        <v>7094084</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1462,10 +1455,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124571960</v>
+        <v>124571916</v>
       </c>
       <c r="B9" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1474,25 +1467,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1500,7 +1493,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1510,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>735822</v>
+        <v>735671</v>
       </c>
       <c r="R9" t="n">
-        <v>7094149</v>
+        <v>7094195</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1572,7 +1565,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124572008</v>
+        <v>124572169</v>
       </c>
       <c r="B10" t="n">
         <v>56722</v>
@@ -1605,12 +1598,20 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>övernattning</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1620,10 +1621,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>735894</v>
+        <v>735753</v>
       </c>
       <c r="R10" t="n">
-        <v>7093968</v>
+        <v>7094155</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1650,12 +1651,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1682,7 +1688,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124572169</v>
+        <v>124571976</v>
       </c>
       <c r="B11" t="n">
         <v>56722</v>
@@ -1715,20 +1721,12 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>övernattning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1738,10 +1736,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>735753</v>
+        <v>735843</v>
       </c>
       <c r="R11" t="n">
-        <v>7094155</v>
+        <v>7093984</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1768,17 +1766,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,7 +1798,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124571973</v>
+        <v>124571918</v>
       </c>
       <c r="B12" t="n">
         <v>56722</v>
@@ -1853,10 +1846,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>735833</v>
+        <v>735703</v>
       </c>
       <c r="R12" t="n">
-        <v>7094015</v>
+        <v>7094102</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1915,7 +1908,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124571918</v>
+        <v>124572048</v>
       </c>
       <c r="B13" t="n">
         <v>56722</v>
@@ -1963,10 +1956,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>735703</v>
+        <v>735905</v>
       </c>
       <c r="R13" t="n">
-        <v>7094102</v>
+        <v>7094143</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2025,10 +2018,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124572048</v>
+        <v>124571954</v>
       </c>
       <c r="B14" t="n">
-        <v>56722</v>
+        <v>57666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2037,33 +2030,37 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2073,10 +2070,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>735905</v>
+        <v>735788</v>
       </c>
       <c r="R14" t="n">
-        <v>7094143</v>
+        <v>7094109</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2135,7 +2132,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124571896</v>
+        <v>124572050</v>
       </c>
       <c r="B15" t="n">
         <v>56722</v>
@@ -2183,10 +2180,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>735546</v>
+        <v>735918</v>
       </c>
       <c r="R15" t="n">
-        <v>7094241</v>
+        <v>7094133</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2219,11 +2216,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Natträd med blindtarmstömning under.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2250,10 +2242,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124572161</v>
+        <v>124571960</v>
       </c>
       <c r="B16" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2262,41 +2254,33 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>övernattning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2306,10 +2290,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>735754</v>
+        <v>735822</v>
       </c>
       <c r="R16" t="n">
-        <v>7094207</v>
+        <v>7094149</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2336,17 +2320,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2373,7 +2352,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124572066</v>
+        <v>124571964</v>
       </c>
       <c r="B17" t="n">
         <v>56722</v>
@@ -2421,10 +2400,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>735937</v>
+        <v>735877</v>
       </c>
       <c r="R17" t="n">
-        <v>7094116</v>
+        <v>7094173</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2457,11 +2436,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ett av flera natträd med nattspillning och blidntarmstömning under. Dessutom kortspillning under detta. Indikerar spelplats i lämplig biotop för spel.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2488,7 +2462,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124571976</v>
+        <v>124572161</v>
       </c>
       <c r="B18" t="n">
         <v>56722</v>
@@ -2521,12 +2495,20 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>övernattning</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2536,10 +2518,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>735843</v>
+        <v>735754</v>
       </c>
       <c r="R18" t="n">
-        <v>7093984</v>
+        <v>7094207</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2566,12 +2548,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2598,7 +2585,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124572050</v>
+        <v>124572176</v>
       </c>
       <c r="B19" t="n">
         <v>56722</v>
@@ -2631,12 +2618,20 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>övernattning</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2646,10 +2641,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>735918</v>
+        <v>735831</v>
       </c>
       <c r="R19" t="n">
-        <v>7094133</v>
+        <v>7094139</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2676,12 +2671,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 4450-2025 artfynd.xlsx
+++ b/artfynd/A 4450-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124571896</v>
+        <v>124571918</v>
       </c>
       <c r="B2" t="n">
         <v>56722</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>735546</v>
+        <v>735703</v>
       </c>
       <c r="R2" t="n">
-        <v>7094241</v>
+        <v>7094102</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,11 +759,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Natträd med blindtarmstömning under.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124571938</v>
+        <v>124572050</v>
       </c>
       <c r="B3" t="n">
         <v>56722</v>
@@ -838,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>735748</v>
+        <v>735918</v>
       </c>
       <c r="R3" t="n">
-        <v>7094125</v>
+        <v>7094133</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,7 +895,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124572066</v>
+        <v>124571964</v>
       </c>
       <c r="B4" t="n">
         <v>56722</v>
@@ -948,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>735937</v>
+        <v>735877</v>
       </c>
       <c r="R4" t="n">
-        <v>7094116</v>
+        <v>7094173</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,11 +979,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ett av flera natträd med nattspillning och blidntarmstömning under. Dessutom kortspillning under detta. Indikerar spelplats i lämplig biotop för spel.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,7 +1005,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124571973</v>
+        <v>124572176</v>
       </c>
       <c r="B5" t="n">
         <v>56722</v>
@@ -1048,12 +1038,20 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>övernattning</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1063,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>735833</v>
+        <v>735831</v>
       </c>
       <c r="R5" t="n">
-        <v>7094015</v>
+        <v>7094139</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,12 +1091,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,7 +1128,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124572008</v>
+        <v>124572068</v>
       </c>
       <c r="B6" t="n">
         <v>56722</v>
@@ -1173,10 +1176,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>735894</v>
+        <v>735946</v>
       </c>
       <c r="R6" t="n">
-        <v>7093968</v>
+        <v>7094100</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1235,10 +1238,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124572068</v>
+        <v>124571954</v>
       </c>
       <c r="B7" t="n">
-        <v>56722</v>
+        <v>57666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,33 +1250,37 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1283,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>735946</v>
+        <v>735788</v>
       </c>
       <c r="R7" t="n">
-        <v>7094100</v>
+        <v>7094109</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,7 +1352,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124572088</v>
+        <v>124572161</v>
       </c>
       <c r="B8" t="n">
         <v>56722</v>
@@ -1378,12 +1385,20 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>övernattning</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1393,10 +1408,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>735949</v>
+        <v>735754</v>
       </c>
       <c r="R8" t="n">
-        <v>7094084</v>
+        <v>7094207</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1423,12 +1438,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1455,7 +1475,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124571916</v>
+        <v>124572169</v>
       </c>
       <c r="B9" t="n">
         <v>56722</v>
@@ -1488,12 +1508,20 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>övernattning</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1503,10 +1531,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>735671</v>
+        <v>735753</v>
       </c>
       <c r="R9" t="n">
-        <v>7094195</v>
+        <v>7094155</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1533,12 +1561,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1565,7 +1598,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124572169</v>
+        <v>124571896</v>
       </c>
       <c r="B10" t="n">
         <v>56722</v>
@@ -1598,20 +1631,12 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>övernattning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1621,10 +1646,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>735753</v>
+        <v>735546</v>
       </c>
       <c r="R10" t="n">
-        <v>7094155</v>
+        <v>7094241</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1651,17 +1676,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
+          <t>Natträd med blindtarmstömning under.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,7 +1713,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124571976</v>
+        <v>124571973</v>
       </c>
       <c r="B11" t="n">
         <v>56722</v>
@@ -1736,10 +1761,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>735843</v>
+        <v>735833</v>
       </c>
       <c r="R11" t="n">
-        <v>7093984</v>
+        <v>7094015</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1798,7 +1823,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124571918</v>
+        <v>124571938</v>
       </c>
       <c r="B12" t="n">
         <v>56722</v>
@@ -1846,10 +1871,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>735703</v>
+        <v>735748</v>
       </c>
       <c r="R12" t="n">
-        <v>7094102</v>
+        <v>7094125</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2018,10 +2043,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124571954</v>
+        <v>124571976</v>
       </c>
       <c r="B14" t="n">
-        <v>57666</v>
+        <v>56722</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2030,37 +2055,33 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2070,10 +2091,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>735788</v>
+        <v>735843</v>
       </c>
       <c r="R14" t="n">
-        <v>7094109</v>
+        <v>7093984</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2132,7 +2153,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124572050</v>
+        <v>124572066</v>
       </c>
       <c r="B15" t="n">
         <v>56722</v>
@@ -2180,10 +2201,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>735918</v>
+        <v>735937</v>
       </c>
       <c r="R15" t="n">
-        <v>7094133</v>
+        <v>7094116</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2216,6 +2237,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ett av flera natträd med nattspillning och blidntarmstömning under. Dessutom kortspillning under detta. Indikerar spelplats i lämplig biotop för spel.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2242,10 +2268,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124571960</v>
+        <v>124572008</v>
       </c>
       <c r="B16" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2254,25 +2280,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2280,7 +2306,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2290,10 +2316,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>735822</v>
+        <v>735894</v>
       </c>
       <c r="R16" t="n">
-        <v>7094149</v>
+        <v>7093968</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2352,7 +2378,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124571964</v>
+        <v>124571916</v>
       </c>
       <c r="B17" t="n">
         <v>56722</v>
@@ -2400,10 +2426,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>735877</v>
+        <v>735671</v>
       </c>
       <c r="R17" t="n">
-        <v>7094173</v>
+        <v>7094195</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2462,10 +2488,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124572161</v>
+        <v>124571960</v>
       </c>
       <c r="B18" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2474,41 +2500,33 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>övernattning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2518,10 +2536,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>735754</v>
+        <v>735822</v>
       </c>
       <c r="R18" t="n">
-        <v>7094207</v>
+        <v>7094149</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2548,17 +2566,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2585,7 +2598,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124572176</v>
+        <v>124572088</v>
       </c>
       <c r="B19" t="n">
         <v>56722</v>
@@ -2618,20 +2631,12 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>övernattning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2641,10 +2646,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>735831</v>
+        <v>735949</v>
       </c>
       <c r="R19" t="n">
-        <v>7094139</v>
+        <v>7094084</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2671,17 +2676,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 4450-2025 artfynd.xlsx
+++ b/artfynd/A 4450-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124571918</v>
+        <v>124571938</v>
       </c>
       <c r="B2" t="n">
         <v>56722</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>735703</v>
+        <v>735748</v>
       </c>
       <c r="R2" t="n">
-        <v>7094102</v>
+        <v>7094125</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124572050</v>
+        <v>124572161</v>
       </c>
       <c r="B3" t="n">
         <v>56722</v>
@@ -818,12 +818,20 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>övernattning</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -833,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>735918</v>
+        <v>735754</v>
       </c>
       <c r="R3" t="n">
-        <v>7094133</v>
+        <v>7094207</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -863,12 +871,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,7 +908,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124571964</v>
+        <v>124572088</v>
       </c>
       <c r="B4" t="n">
         <v>56722</v>
@@ -943,10 +956,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>735877</v>
+        <v>735949</v>
       </c>
       <c r="R4" t="n">
-        <v>7094173</v>
+        <v>7094084</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,7 +1018,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124572176</v>
+        <v>124571973</v>
       </c>
       <c r="B5" t="n">
         <v>56722</v>
@@ -1038,20 +1051,12 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>övernattning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1061,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>735831</v>
+        <v>735833</v>
       </c>
       <c r="R5" t="n">
-        <v>7094139</v>
+        <v>7094015</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,17 +1096,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,7 +1128,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124572068</v>
+        <v>124572169</v>
       </c>
       <c r="B6" t="n">
         <v>56722</v>
@@ -1161,12 +1161,20 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>övernattning</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1176,10 +1184,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>735946</v>
+        <v>735753</v>
       </c>
       <c r="R6" t="n">
-        <v>7094100</v>
+        <v>7094155</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,12 +1214,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,10 +1251,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124571954</v>
+        <v>124572176</v>
       </c>
       <c r="B7" t="n">
-        <v>57666</v>
+        <v>56722</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,25 +1263,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1277,10 +1290,14 @@
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>övernattning</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1290,10 +1307,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>735788</v>
+        <v>735831</v>
       </c>
       <c r="R7" t="n">
-        <v>7094109</v>
+        <v>7094139</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,12 +1337,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,7 +1374,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124572161</v>
+        <v>124571916</v>
       </c>
       <c r="B8" t="n">
         <v>56722</v>
@@ -1385,20 +1407,12 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>övernattning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1408,10 +1422,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>735754</v>
+        <v>735671</v>
       </c>
       <c r="R8" t="n">
-        <v>7094207</v>
+        <v>7094195</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1438,17 +1452,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1475,7 +1484,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124572169</v>
+        <v>124572066</v>
       </c>
       <c r="B9" t="n">
         <v>56722</v>
@@ -1508,20 +1517,12 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>övernattning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1531,10 +1532,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>735753</v>
+        <v>735937</v>
       </c>
       <c r="R9" t="n">
-        <v>7094155</v>
+        <v>7094116</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1561,17 +1562,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
+          <t>Ett av flera natträd med nattspillning och blidntarmstömning under. Dessutom kortspillning under detta. Indikerar spelplats i lämplig biotop för spel.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1598,7 +1599,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124571896</v>
+        <v>124572048</v>
       </c>
       <c r="B10" t="n">
         <v>56722</v>
@@ -1646,10 +1647,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>735546</v>
+        <v>735905</v>
       </c>
       <c r="R10" t="n">
-        <v>7094241</v>
+        <v>7094143</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1682,11 +1683,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Natträd med blindtarmstömning under.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1713,10 +1709,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124571973</v>
+        <v>124571954</v>
       </c>
       <c r="B11" t="n">
-        <v>56722</v>
+        <v>57666</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1725,33 +1721,37 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1761,10 +1761,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>735833</v>
+        <v>735788</v>
       </c>
       <c r="R11" t="n">
-        <v>7094015</v>
+        <v>7094109</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1823,7 +1823,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124571938</v>
+        <v>124571976</v>
       </c>
       <c r="B12" t="n">
         <v>56722</v>
@@ -1871,10 +1871,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>735748</v>
+        <v>735843</v>
       </c>
       <c r="R12" t="n">
-        <v>7094125</v>
+        <v>7093984</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1933,7 +1933,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124572048</v>
+        <v>124572050</v>
       </c>
       <c r="B13" t="n">
         <v>56722</v>
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>735905</v>
+        <v>735918</v>
       </c>
       <c r="R13" t="n">
-        <v>7094143</v>
+        <v>7094133</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2043,10 +2043,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124571976</v>
+        <v>124571960</v>
       </c>
       <c r="B14" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2055,25 +2055,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2081,7 +2081,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2091,10 +2091,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>735843</v>
+        <v>735822</v>
       </c>
       <c r="R14" t="n">
-        <v>7093984</v>
+        <v>7094149</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2153,7 +2153,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124572066</v>
+        <v>124572068</v>
       </c>
       <c r="B15" t="n">
         <v>56722</v>
@@ -2201,10 +2201,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>735937</v>
+        <v>735946</v>
       </c>
       <c r="R15" t="n">
-        <v>7094116</v>
+        <v>7094100</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2237,11 +2237,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ett av flera natträd med nattspillning och blidntarmstömning under. Dessutom kortspillning under detta. Indikerar spelplats i lämplig biotop för spel.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2268,7 +2263,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124572008</v>
+        <v>124571896</v>
       </c>
       <c r="B16" t="n">
         <v>56722</v>
@@ -2316,10 +2311,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>735894</v>
+        <v>735546</v>
       </c>
       <c r="R16" t="n">
-        <v>7093968</v>
+        <v>7094241</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2352,6 +2347,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Natträd med blindtarmstömning under.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2378,7 +2378,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124571916</v>
+        <v>124571918</v>
       </c>
       <c r="B17" t="n">
         <v>56722</v>
@@ -2426,10 +2426,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>735671</v>
+        <v>735703</v>
       </c>
       <c r="R17" t="n">
-        <v>7094195</v>
+        <v>7094102</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2488,10 +2488,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124571960</v>
+        <v>124571964</v>
       </c>
       <c r="B18" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2500,25 +2500,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2526,7 +2526,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2536,10 +2536,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>735822</v>
+        <v>735877</v>
       </c>
       <c r="R18" t="n">
-        <v>7094149</v>
+        <v>7094173</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2598,7 +2598,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124572088</v>
+        <v>124572008</v>
       </c>
       <c r="B19" t="n">
         <v>56722</v>
@@ -2646,10 +2646,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>735949</v>
+        <v>735894</v>
       </c>
       <c r="R19" t="n">
-        <v>7094084</v>
+        <v>7093968</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 4450-2025 artfynd.xlsx
+++ b/artfynd/A 4450-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124571938</v>
+        <v>124571960</v>
       </c>
       <c r="B2" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,7 +713,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>735748</v>
+        <v>735822</v>
       </c>
       <c r="R2" t="n">
-        <v>7094125</v>
+        <v>7094149</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124572161</v>
+        <v>124572088</v>
       </c>
       <c r="B3" t="n">
         <v>56722</v>
@@ -818,20 +818,12 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>övernattning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -841,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>735754</v>
+        <v>735949</v>
       </c>
       <c r="R3" t="n">
-        <v>7094207</v>
+        <v>7094084</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,17 +863,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,7 +895,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124572088</v>
+        <v>124572161</v>
       </c>
       <c r="B4" t="n">
         <v>56722</v>
@@ -941,12 +928,20 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>övernattning</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -956,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>735949</v>
+        <v>735754</v>
       </c>
       <c r="R4" t="n">
-        <v>7094084</v>
+        <v>7094207</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,12 +981,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,7 +1018,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124571973</v>
+        <v>124572169</v>
       </c>
       <c r="B5" t="n">
         <v>56722</v>
@@ -1051,12 +1051,20 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>övernattning</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1066,10 +1074,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>735833</v>
+        <v>735753</v>
       </c>
       <c r="R5" t="n">
-        <v>7094015</v>
+        <v>7094155</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,12 +1104,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,7 +1141,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124572169</v>
+        <v>124571973</v>
       </c>
       <c r="B6" t="n">
         <v>56722</v>
@@ -1161,20 +1174,12 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>övernattning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1184,10 +1189,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>735753</v>
+        <v>735833</v>
       </c>
       <c r="R6" t="n">
-        <v>7094155</v>
+        <v>7094015</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1214,17 +1219,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1251,7 +1251,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124572176</v>
+        <v>124572008</v>
       </c>
       <c r="B7" t="n">
         <v>56722</v>
@@ -1284,20 +1284,12 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>övernattning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1307,10 +1299,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>735831</v>
+        <v>735894</v>
       </c>
       <c r="R7" t="n">
-        <v>7094139</v>
+        <v>7093968</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1337,17 +1329,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,10 +1361,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124571916</v>
+        <v>124571954</v>
       </c>
       <c r="B8" t="n">
-        <v>56722</v>
+        <v>57666</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1386,33 +1373,37 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1422,10 +1413,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>735671</v>
+        <v>735788</v>
       </c>
       <c r="R8" t="n">
-        <v>7094195</v>
+        <v>7094109</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1484,7 +1475,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124572066</v>
+        <v>124572048</v>
       </c>
       <c r="B9" t="n">
         <v>56722</v>
@@ -1532,10 +1523,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>735937</v>
+        <v>735905</v>
       </c>
       <c r="R9" t="n">
-        <v>7094116</v>
+        <v>7094143</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1568,11 +1559,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ett av flera natträd med nattspillning och blidntarmstömning under. Dessutom kortspillning under detta. Indikerar spelplats i lämplig biotop för spel.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1599,7 +1585,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124572048</v>
+        <v>124571976</v>
       </c>
       <c r="B10" t="n">
         <v>56722</v>
@@ -1647,10 +1633,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>735905</v>
+        <v>735843</v>
       </c>
       <c r="R10" t="n">
-        <v>7094143</v>
+        <v>7093984</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1709,10 +1695,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124571954</v>
+        <v>124572176</v>
       </c>
       <c r="B11" t="n">
-        <v>57666</v>
+        <v>56722</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1721,25 +1707,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1748,10 +1734,14 @@
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>övernattning</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1761,10 +1751,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>735788</v>
+        <v>735831</v>
       </c>
       <c r="R11" t="n">
-        <v>7094109</v>
+        <v>7094139</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1791,12 +1781,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1823,7 +1818,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124571976</v>
+        <v>124571896</v>
       </c>
       <c r="B12" t="n">
         <v>56722</v>
@@ -1871,10 +1866,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>735843</v>
+        <v>735546</v>
       </c>
       <c r="R12" t="n">
-        <v>7093984</v>
+        <v>7094241</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,6 +1902,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Natträd med blindtarmstömning under.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2043,10 +2043,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124571960</v>
+        <v>124572066</v>
       </c>
       <c r="B14" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2055,25 +2055,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2081,7 +2081,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2091,10 +2091,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>735822</v>
+        <v>735937</v>
       </c>
       <c r="R14" t="n">
-        <v>7094149</v>
+        <v>7094116</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2127,6 +2127,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ett av flera natträd med nattspillning och blidntarmstömning under. Dessutom kortspillning under detta. Indikerar spelplats i lämplig biotop för spel.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2153,7 +2158,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124572068</v>
+        <v>124571916</v>
       </c>
       <c r="B15" t="n">
         <v>56722</v>
@@ -2201,10 +2206,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>735946</v>
+        <v>735671</v>
       </c>
       <c r="R15" t="n">
-        <v>7094100</v>
+        <v>7094195</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2263,7 +2268,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124571896</v>
+        <v>124572068</v>
       </c>
       <c r="B16" t="n">
         <v>56722</v>
@@ -2311,10 +2316,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>735546</v>
+        <v>735946</v>
       </c>
       <c r="R16" t="n">
-        <v>7094241</v>
+        <v>7094100</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2347,11 +2352,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Natträd med blindtarmstömning under.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2378,7 +2378,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124571918</v>
+        <v>124571964</v>
       </c>
       <c r="B17" t="n">
         <v>56722</v>
@@ -2426,10 +2426,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>735703</v>
+        <v>735877</v>
       </c>
       <c r="R17" t="n">
-        <v>7094102</v>
+        <v>7094173</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2488,7 +2488,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124571964</v>
+        <v>124571918</v>
       </c>
       <c r="B18" t="n">
         <v>56722</v>
@@ -2536,10 +2536,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>735877</v>
+        <v>735703</v>
       </c>
       <c r="R18" t="n">
-        <v>7094173</v>
+        <v>7094102</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2598,7 +2598,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124572008</v>
+        <v>124571938</v>
       </c>
       <c r="B19" t="n">
         <v>56722</v>
@@ -2646,10 +2646,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>735894</v>
+        <v>735748</v>
       </c>
       <c r="R19" t="n">
-        <v>7093968</v>
+        <v>7094125</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 4450-2025 artfynd.xlsx
+++ b/artfynd/A 4450-2025 artfynd.xlsx
@@ -1695,7 +1695,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124572176</v>
+        <v>124571896</v>
       </c>
       <c r="B11" t="n">
         <v>56722</v>
@@ -1728,20 +1728,12 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>övernattning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1751,10 +1743,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>735831</v>
+        <v>735546</v>
       </c>
       <c r="R11" t="n">
-        <v>7094139</v>
+        <v>7094241</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1781,17 +1773,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
+          <t>Natträd med blindtarmstömning under.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1818,7 +1810,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124571896</v>
+        <v>124572176</v>
       </c>
       <c r="B12" t="n">
         <v>56722</v>
@@ -1851,12 +1843,20 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>övernattning</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>735546</v>
+        <v>735831</v>
       </c>
       <c r="R12" t="n">
-        <v>7094241</v>
+        <v>7094139</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1896,17 +1896,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Natträd med blindtarmstömning under.</t>
+          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 4450-2025 artfynd.xlsx
+++ b/artfynd/A 4450-2025 artfynd.xlsx
@@ -2378,7 +2378,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124571964</v>
+        <v>124571918</v>
       </c>
       <c r="B17" t="n">
         <v>56722</v>
@@ -2426,10 +2426,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>735877</v>
+        <v>735703</v>
       </c>
       <c r="R17" t="n">
-        <v>7094173</v>
+        <v>7094102</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2488,7 +2488,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124571918</v>
+        <v>124571964</v>
       </c>
       <c r="B18" t="n">
         <v>56722</v>
@@ -2536,10 +2536,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>735703</v>
+        <v>735877</v>
       </c>
       <c r="R18" t="n">
-        <v>7094102</v>
+        <v>7094173</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 4450-2025 artfynd.xlsx
+++ b/artfynd/A 4450-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124571960</v>
+        <v>124571916</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,7 +713,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>735822</v>
+        <v>735671</v>
       </c>
       <c r="R2" t="n">
-        <v>7094149</v>
+        <v>7094195</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124572088</v>
+        <v>124572169</v>
       </c>
       <c r="B3" t="n">
         <v>56722</v>
@@ -818,12 +818,20 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>övernattning</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -833,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>735949</v>
+        <v>735753</v>
       </c>
       <c r="R3" t="n">
-        <v>7094084</v>
+        <v>7094155</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -863,12 +871,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,7 +908,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124572161</v>
+        <v>124571964</v>
       </c>
       <c r="B4" t="n">
         <v>56722</v>
@@ -928,20 +941,12 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>övernattning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -951,10 +956,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>735754</v>
+        <v>735877</v>
       </c>
       <c r="R4" t="n">
-        <v>7094207</v>
+        <v>7094173</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,17 +986,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,7 +1018,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124572169</v>
+        <v>124571938</v>
       </c>
       <c r="B5" t="n">
         <v>56722</v>
@@ -1051,20 +1051,12 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>övernattning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1074,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>735753</v>
+        <v>735748</v>
       </c>
       <c r="R5" t="n">
-        <v>7094155</v>
+        <v>7094125</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,17 +1096,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,7 +1128,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124571973</v>
+        <v>124572068</v>
       </c>
       <c r="B6" t="n">
         <v>56722</v>
@@ -1189,10 +1176,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>735833</v>
+        <v>735946</v>
       </c>
       <c r="R6" t="n">
-        <v>7094015</v>
+        <v>7094100</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1361,10 +1348,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124571954</v>
+        <v>124571896</v>
       </c>
       <c r="B8" t="n">
-        <v>57666</v>
+        <v>56722</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,37 +1360,33 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1413,10 +1396,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>735788</v>
+        <v>735546</v>
       </c>
       <c r="R8" t="n">
-        <v>7094109</v>
+        <v>7094241</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1449,6 +1432,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Natträd med blindtarmstömning under.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1475,7 +1463,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124572048</v>
+        <v>124572161</v>
       </c>
       <c r="B9" t="n">
         <v>56722</v>
@@ -1508,12 +1496,20 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>övernattning</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1523,10 +1519,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>735905</v>
+        <v>735754</v>
       </c>
       <c r="R9" t="n">
-        <v>7094143</v>
+        <v>7094207</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1553,12 +1549,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,7 +1586,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124571976</v>
+        <v>124572088</v>
       </c>
       <c r="B10" t="n">
         <v>56722</v>
@@ -1633,10 +1634,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>735843</v>
+        <v>735949</v>
       </c>
       <c r="R10" t="n">
-        <v>7093984</v>
+        <v>7094084</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1695,7 +1696,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124571896</v>
+        <v>124572050</v>
       </c>
       <c r="B11" t="n">
         <v>56722</v>
@@ -1743,10 +1744,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>735546</v>
+        <v>735918</v>
       </c>
       <c r="R11" t="n">
-        <v>7094241</v>
+        <v>7094133</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1779,11 +1780,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Natträd med blindtarmstömning under.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1933,10 +1929,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124572050</v>
+        <v>124571960</v>
       </c>
       <c r="B13" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1945,25 +1941,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1971,7 +1967,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1981,10 +1977,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>735918</v>
+        <v>735822</v>
       </c>
       <c r="R13" t="n">
-        <v>7094133</v>
+        <v>7094149</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2043,7 +2039,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124572066</v>
+        <v>124571918</v>
       </c>
       <c r="B14" t="n">
         <v>56722</v>
@@ -2091,10 +2087,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>735937</v>
+        <v>735703</v>
       </c>
       <c r="R14" t="n">
-        <v>7094116</v>
+        <v>7094102</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2127,11 +2123,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ett av flera natträd med nattspillning och blidntarmstömning under. Dessutom kortspillning under detta. Indikerar spelplats i lämplig biotop för spel.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2158,7 +2149,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124571916</v>
+        <v>124572066</v>
       </c>
       <c r="B15" t="n">
         <v>56722</v>
@@ -2206,10 +2197,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>735671</v>
+        <v>735937</v>
       </c>
       <c r="R15" t="n">
-        <v>7094195</v>
+        <v>7094116</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2242,6 +2233,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ett av flera natträd med nattspillning och blidntarmstömning under. Dessutom kortspillning under detta. Indikerar spelplats i lämplig biotop för spel.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2268,7 +2264,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124572068</v>
+        <v>124571973</v>
       </c>
       <c r="B16" t="n">
         <v>56722</v>
@@ -2316,10 +2312,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>735946</v>
+        <v>735833</v>
       </c>
       <c r="R16" t="n">
-        <v>7094100</v>
+        <v>7094015</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2378,10 +2374,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124571918</v>
+        <v>124571954</v>
       </c>
       <c r="B17" t="n">
-        <v>56722</v>
+        <v>57666</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2390,33 +2386,37 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2426,10 +2426,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>735703</v>
+        <v>735788</v>
       </c>
       <c r="R17" t="n">
-        <v>7094102</v>
+        <v>7094109</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2488,7 +2488,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124571964</v>
+        <v>124571976</v>
       </c>
       <c r="B18" t="n">
         <v>56722</v>
@@ -2536,10 +2536,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>735877</v>
+        <v>735843</v>
       </c>
       <c r="R18" t="n">
-        <v>7094173</v>
+        <v>7093984</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2598,7 +2598,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124571938</v>
+        <v>124572048</v>
       </c>
       <c r="B19" t="n">
         <v>56722</v>
@@ -2646,10 +2646,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>735748</v>
+        <v>735905</v>
       </c>
       <c r="R19" t="n">
-        <v>7094125</v>
+        <v>7094143</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 4450-2025 artfynd.xlsx
+++ b/artfynd/A 4450-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124571916</v>
+        <v>124571973</v>
       </c>
       <c r="B2" t="n">
         <v>56722</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>735671</v>
+        <v>735833</v>
       </c>
       <c r="R2" t="n">
-        <v>7094195</v>
+        <v>7094015</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124572169</v>
+        <v>124572068</v>
       </c>
       <c r="B3" t="n">
         <v>56722</v>
@@ -818,20 +818,12 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>övernattning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -841,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>735753</v>
+        <v>735946</v>
       </c>
       <c r="R3" t="n">
-        <v>7094155</v>
+        <v>7094100</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,17 +863,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124571964</v>
+        <v>124571954</v>
       </c>
       <c r="B4" t="n">
-        <v>56722</v>
+        <v>57666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,33 +907,37 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -956,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>735877</v>
+        <v>735788</v>
       </c>
       <c r="R4" t="n">
-        <v>7094173</v>
+        <v>7094109</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1018,7 +1009,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124571938</v>
+        <v>124572161</v>
       </c>
       <c r="B5" t="n">
         <v>56722</v>
@@ -1051,12 +1042,20 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>övernattning</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1066,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>735748</v>
+        <v>735754</v>
       </c>
       <c r="R5" t="n">
-        <v>7094125</v>
+        <v>7094207</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,12 +1095,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,7 +1132,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124572068</v>
+        <v>124571918</v>
       </c>
       <c r="B6" t="n">
         <v>56722</v>
@@ -1176,10 +1180,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>735946</v>
+        <v>735703</v>
       </c>
       <c r="R6" t="n">
-        <v>7094100</v>
+        <v>7094102</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1238,7 +1242,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124572008</v>
+        <v>124572050</v>
       </c>
       <c r="B7" t="n">
         <v>56722</v>
@@ -1286,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>735894</v>
+        <v>735918</v>
       </c>
       <c r="R7" t="n">
-        <v>7093968</v>
+        <v>7094133</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1348,7 +1352,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124571896</v>
+        <v>124572048</v>
       </c>
       <c r="B8" t="n">
         <v>56722</v>
@@ -1396,10 +1400,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>735546</v>
+        <v>735905</v>
       </c>
       <c r="R8" t="n">
-        <v>7094241</v>
+        <v>7094143</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1432,11 +1436,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Natträd med blindtarmstömning under.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,7 +1462,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124572161</v>
+        <v>124571896</v>
       </c>
       <c r="B9" t="n">
         <v>56722</v>
@@ -1496,20 +1495,12 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>övernattning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1519,10 +1510,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>735754</v>
+        <v>735546</v>
       </c>
       <c r="R9" t="n">
-        <v>7094207</v>
+        <v>7094241</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1549,17 +1540,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
+          <t>Natträd med blindtarmstömning under.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,7 +1577,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124572088</v>
+        <v>124572169</v>
       </c>
       <c r="B10" t="n">
         <v>56722</v>
@@ -1619,12 +1610,20 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>övernattning</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1634,10 +1633,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>735949</v>
+        <v>735753</v>
       </c>
       <c r="R10" t="n">
-        <v>7094084</v>
+        <v>7094155</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1664,12 +1663,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,7 +1700,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124572050</v>
+        <v>124571938</v>
       </c>
       <c r="B11" t="n">
         <v>56722</v>
@@ -1744,10 +1748,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>735918</v>
+        <v>735748</v>
       </c>
       <c r="R11" t="n">
-        <v>7094133</v>
+        <v>7094125</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1806,7 +1810,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124572176</v>
+        <v>124571916</v>
       </c>
       <c r="B12" t="n">
         <v>56722</v>
@@ -1839,20 +1843,12 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>övernattning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1862,10 +1858,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>735831</v>
+        <v>735671</v>
       </c>
       <c r="R12" t="n">
-        <v>7094139</v>
+        <v>7094195</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1892,17 +1888,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1929,10 +1920,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124571960</v>
+        <v>124571964</v>
       </c>
       <c r="B13" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1941,25 +1932,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1967,7 +1958,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1977,10 +1968,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>735822</v>
+        <v>735877</v>
       </c>
       <c r="R13" t="n">
-        <v>7094149</v>
+        <v>7094173</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2039,7 +2030,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124571918</v>
+        <v>124572008</v>
       </c>
       <c r="B14" t="n">
         <v>56722</v>
@@ -2087,10 +2078,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>735703</v>
+        <v>735894</v>
       </c>
       <c r="R14" t="n">
-        <v>7094102</v>
+        <v>7093968</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2149,7 +2140,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124572066</v>
+        <v>124571976</v>
       </c>
       <c r="B15" t="n">
         <v>56722</v>
@@ -2197,10 +2188,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>735937</v>
+        <v>735843</v>
       </c>
       <c r="R15" t="n">
-        <v>7094116</v>
+        <v>7093984</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2233,11 +2224,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ett av flera natträd med nattspillning och blidntarmstömning under. Dessutom kortspillning under detta. Indikerar spelplats i lämplig biotop för spel.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2264,7 +2250,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124571973</v>
+        <v>124572088</v>
       </c>
       <c r="B16" t="n">
         <v>56722</v>
@@ -2312,10 +2298,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>735833</v>
+        <v>735949</v>
       </c>
       <c r="R16" t="n">
-        <v>7094015</v>
+        <v>7094084</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2374,10 +2360,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124571954</v>
+        <v>124572176</v>
       </c>
       <c r="B17" t="n">
-        <v>57666</v>
+        <v>56722</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2386,25 +2372,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2413,10 +2399,14 @@
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>övernattning</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2426,10 +2416,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>735788</v>
+        <v>735831</v>
       </c>
       <c r="R17" t="n">
-        <v>7094109</v>
+        <v>7094139</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2456,12 +2446,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2488,7 +2483,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124571976</v>
+        <v>124572066</v>
       </c>
       <c r="B18" t="n">
         <v>56722</v>
@@ -2536,10 +2531,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>735843</v>
+        <v>735937</v>
       </c>
       <c r="R18" t="n">
-        <v>7093984</v>
+        <v>7094116</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2572,6 +2567,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ett av flera natträd med nattspillning och blidntarmstömning under. Dessutom kortspillning under detta. Indikerar spelplats i lämplig biotop för spel.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2598,10 +2598,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124572048</v>
+        <v>124571960</v>
       </c>
       <c r="B19" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2610,25 +2610,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2636,7 +2636,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2646,10 +2646,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>735905</v>
+        <v>735822</v>
       </c>
       <c r="R19" t="n">
-        <v>7094143</v>
+        <v>7094149</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 4450-2025 artfynd.xlsx
+++ b/artfynd/A 4450-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124571973</v>
+        <v>124571954</v>
       </c>
       <c r="B2" t="n">
-        <v>56722</v>
+        <v>57666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,33 +687,37 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -723,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>735833</v>
+        <v>735788</v>
       </c>
       <c r="R2" t="n">
-        <v>7094015</v>
+        <v>7094109</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,7 +789,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124572068</v>
+        <v>124572088</v>
       </c>
       <c r="B3" t="n">
         <v>56722</v>
@@ -833,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>735946</v>
+        <v>735949</v>
       </c>
       <c r="R3" t="n">
-        <v>7094100</v>
+        <v>7094084</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124571954</v>
+        <v>124572008</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>56722</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,37 +911,33 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>735788</v>
+        <v>735894</v>
       </c>
       <c r="R4" t="n">
-        <v>7094109</v>
+        <v>7093968</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,7 +1009,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124572161</v>
+        <v>124572050</v>
       </c>
       <c r="B5" t="n">
         <v>56722</v>
@@ -1042,20 +1042,12 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>övernattning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1065,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>735754</v>
+        <v>735918</v>
       </c>
       <c r="R5" t="n">
-        <v>7094207</v>
+        <v>7094133</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,17 +1087,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124571918</v>
+        <v>124572176</v>
       </c>
       <c r="B6" t="n">
         <v>56722</v>
@@ -1165,12 +1152,20 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>övernattning</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1180,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>735703</v>
+        <v>735831</v>
       </c>
       <c r="R6" t="n">
-        <v>7094102</v>
+        <v>7094139</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,12 +1205,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,10 +1242,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124572050</v>
+        <v>124571960</v>
       </c>
       <c r="B7" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1254,25 +1254,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1280,7 +1280,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1290,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>735918</v>
+        <v>735822</v>
       </c>
       <c r="R7" t="n">
-        <v>7094133</v>
+        <v>7094149</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1352,7 +1352,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124572048</v>
+        <v>124572161</v>
       </c>
       <c r="B8" t="n">
         <v>56722</v>
@@ -1385,12 +1385,20 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>övernattning</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1400,10 +1408,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>735905</v>
+        <v>735754</v>
       </c>
       <c r="R8" t="n">
-        <v>7094143</v>
+        <v>7094207</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1430,12 +1438,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1462,7 +1475,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124571896</v>
+        <v>124571916</v>
       </c>
       <c r="B9" t="n">
         <v>56722</v>
@@ -1510,10 +1523,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>735546</v>
+        <v>735671</v>
       </c>
       <c r="R9" t="n">
-        <v>7094241</v>
+        <v>7094195</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1546,11 +1559,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Natträd med blindtarmstömning under.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1700,7 +1708,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124571938</v>
+        <v>124571973</v>
       </c>
       <c r="B11" t="n">
         <v>56722</v>
@@ -1748,10 +1756,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>735748</v>
+        <v>735833</v>
       </c>
       <c r="R11" t="n">
-        <v>7094125</v>
+        <v>7094015</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1810,7 +1818,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124571916</v>
+        <v>124571938</v>
       </c>
       <c r="B12" t="n">
         <v>56722</v>
@@ -1858,10 +1866,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>735671</v>
+        <v>735748</v>
       </c>
       <c r="R12" t="n">
-        <v>7094195</v>
+        <v>7094125</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1920,7 +1928,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124571964</v>
+        <v>124572048</v>
       </c>
       <c r="B13" t="n">
         <v>56722</v>
@@ -1968,10 +1976,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>735877</v>
+        <v>735905</v>
       </c>
       <c r="R13" t="n">
-        <v>7094173</v>
+        <v>7094143</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2030,7 +2038,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124572008</v>
+        <v>124571976</v>
       </c>
       <c r="B14" t="n">
         <v>56722</v>
@@ -2078,10 +2086,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>735894</v>
+        <v>735843</v>
       </c>
       <c r="R14" t="n">
-        <v>7093968</v>
+        <v>7093984</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2140,7 +2148,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124571976</v>
+        <v>124571918</v>
       </c>
       <c r="B15" t="n">
         <v>56722</v>
@@ -2188,10 +2196,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>735843</v>
+        <v>735703</v>
       </c>
       <c r="R15" t="n">
-        <v>7093984</v>
+        <v>7094102</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2250,7 +2258,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124572088</v>
+        <v>124571964</v>
       </c>
       <c r="B16" t="n">
         <v>56722</v>
@@ -2298,10 +2306,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>735949</v>
+        <v>735877</v>
       </c>
       <c r="R16" t="n">
-        <v>7094084</v>
+        <v>7094173</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2360,7 +2368,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124572176</v>
+        <v>124572066</v>
       </c>
       <c r="B17" t="n">
         <v>56722</v>
@@ -2393,20 +2401,12 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>övernattning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2416,10 +2416,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>735831</v>
+        <v>735937</v>
       </c>
       <c r="R17" t="n">
-        <v>7094139</v>
+        <v>7094116</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2446,17 +2446,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
+          <t>Ett av flera natträd med nattspillning och blidntarmstömning under. Dessutom kortspillning under detta. Indikerar spelplats i lämplig biotop för spel.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2483,7 +2483,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124572066</v>
+        <v>124572068</v>
       </c>
       <c r="B18" t="n">
         <v>56722</v>
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>735937</v>
+        <v>735946</v>
       </c>
       <c r="R18" t="n">
-        <v>7094116</v>
+        <v>7094100</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2567,11 +2567,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ett av flera natträd med nattspillning och blidntarmstömning under. Dessutom kortspillning under detta. Indikerar spelplats i lämplig biotop för spel.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2598,10 +2593,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124571960</v>
+        <v>124571896</v>
       </c>
       <c r="B19" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2610,25 +2605,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2636,7 +2631,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2646,10 +2641,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>735822</v>
+        <v>735546</v>
       </c>
       <c r="R19" t="n">
-        <v>7094149</v>
+        <v>7094241</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2682,6 +2677,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Natträd med blindtarmstömning under.</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 4450-2025 artfynd.xlsx
+++ b/artfynd/A 4450-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124571954</v>
+        <v>124572048</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
+        <v>56722</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,37 +687,33 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>735788</v>
+        <v>735905</v>
       </c>
       <c r="R2" t="n">
-        <v>7094109</v>
+        <v>7094143</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124572088</v>
+        <v>124571918</v>
       </c>
       <c r="B3" t="n">
         <v>56722</v>
@@ -837,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>735949</v>
+        <v>735703</v>
       </c>
       <c r="R3" t="n">
-        <v>7094084</v>
+        <v>7094102</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -899,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124572008</v>
+        <v>124571954</v>
       </c>
       <c r="B4" t="n">
-        <v>56722</v>
+        <v>57666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,33 +907,37 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>735894</v>
+        <v>735788</v>
       </c>
       <c r="R4" t="n">
-        <v>7093968</v>
+        <v>7094109</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,7 +1009,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124572050</v>
+        <v>124571976</v>
       </c>
       <c r="B5" t="n">
         <v>56722</v>
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>735918</v>
+        <v>735843</v>
       </c>
       <c r="R5" t="n">
-        <v>7094133</v>
+        <v>7093984</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1242,10 +1242,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124571960</v>
+        <v>124571916</v>
       </c>
       <c r="B7" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1254,25 +1254,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1280,7 +1280,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1290,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>735822</v>
+        <v>735671</v>
       </c>
       <c r="R7" t="n">
-        <v>7094149</v>
+        <v>7094195</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1352,7 +1352,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124572161</v>
+        <v>124572066</v>
       </c>
       <c r="B8" t="n">
         <v>56722</v>
@@ -1385,20 +1385,12 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>övernattning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1408,10 +1400,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>735754</v>
+        <v>735937</v>
       </c>
       <c r="R8" t="n">
-        <v>7094207</v>
+        <v>7094116</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1438,17 +1430,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
+          <t>Ett av flera natträd med nattspillning och blidntarmstömning under. Dessutom kortspillning under detta. Indikerar spelplats i lämplig biotop för spel.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1475,7 +1467,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124571916</v>
+        <v>124572008</v>
       </c>
       <c r="B9" t="n">
         <v>56722</v>
@@ -1523,10 +1515,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>735671</v>
+        <v>735894</v>
       </c>
       <c r="R9" t="n">
-        <v>7094195</v>
+        <v>7093968</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1585,7 +1577,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124572169</v>
+        <v>124572161</v>
       </c>
       <c r="B10" t="n">
         <v>56722</v>
@@ -1641,10 +1633,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>735753</v>
+        <v>735754</v>
       </c>
       <c r="R10" t="n">
-        <v>7094155</v>
+        <v>7094207</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1708,7 +1700,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124571973</v>
+        <v>124571938</v>
       </c>
       <c r="B11" t="n">
         <v>56722</v>
@@ -1756,10 +1748,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>735833</v>
+        <v>735748</v>
       </c>
       <c r="R11" t="n">
-        <v>7094015</v>
+        <v>7094125</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1818,7 +1810,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124571938</v>
+        <v>124572169</v>
       </c>
       <c r="B12" t="n">
         <v>56722</v>
@@ -1851,12 +1843,20 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>övernattning</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>735748</v>
+        <v>735753</v>
       </c>
       <c r="R12" t="n">
-        <v>7094125</v>
+        <v>7094155</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1896,12 +1896,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1928,7 +1933,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124572048</v>
+        <v>124571964</v>
       </c>
       <c r="B13" t="n">
         <v>56722</v>
@@ -1976,10 +1981,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>735905</v>
+        <v>735877</v>
       </c>
       <c r="R13" t="n">
-        <v>7094143</v>
+        <v>7094173</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2038,10 +2043,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124571976</v>
+        <v>124571960</v>
       </c>
       <c r="B14" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2050,25 +2055,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2076,7 +2081,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2086,10 +2091,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>735843</v>
+        <v>735822</v>
       </c>
       <c r="R14" t="n">
-        <v>7093984</v>
+        <v>7094149</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2148,7 +2153,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124571918</v>
+        <v>124572068</v>
       </c>
       <c r="B15" t="n">
         <v>56722</v>
@@ -2196,10 +2201,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>735703</v>
+        <v>735946</v>
       </c>
       <c r="R15" t="n">
-        <v>7094102</v>
+        <v>7094100</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2258,7 +2263,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124571964</v>
+        <v>124571896</v>
       </c>
       <c r="B16" t="n">
         <v>56722</v>
@@ -2306,10 +2311,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>735877</v>
+        <v>735546</v>
       </c>
       <c r="R16" t="n">
-        <v>7094173</v>
+        <v>7094241</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2342,6 +2347,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Natträd med blindtarmstömning under.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2368,7 +2378,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124572066</v>
+        <v>124572088</v>
       </c>
       <c r="B17" t="n">
         <v>56722</v>
@@ -2416,10 +2426,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>735937</v>
+        <v>735949</v>
       </c>
       <c r="R17" t="n">
-        <v>7094116</v>
+        <v>7094084</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2452,11 +2462,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ett av flera natträd med nattspillning och blidntarmstömning under. Dessutom kortspillning under detta. Indikerar spelplats i lämplig biotop för spel.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2483,7 +2488,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124572068</v>
+        <v>124572050</v>
       </c>
       <c r="B18" t="n">
         <v>56722</v>
@@ -2531,10 +2536,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>735946</v>
+        <v>735918</v>
       </c>
       <c r="R18" t="n">
-        <v>7094100</v>
+        <v>7094133</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2593,7 +2598,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124571896</v>
+        <v>124571973</v>
       </c>
       <c r="B19" t="n">
         <v>56722</v>
@@ -2641,10 +2646,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>735546</v>
+        <v>735833</v>
       </c>
       <c r="R19" t="n">
-        <v>7094241</v>
+        <v>7094015</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2677,11 +2682,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Natträd med blindtarmstömning under.</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 4450-2025 artfynd.xlsx
+++ b/artfynd/A 4450-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124572048</v>
+        <v>124572161</v>
       </c>
       <c r="B2" t="n">
         <v>56722</v>
@@ -708,12 +708,20 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>övernattning</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -723,10 +731,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>735905</v>
+        <v>735754</v>
       </c>
       <c r="R2" t="n">
-        <v>7094143</v>
+        <v>7094207</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,12 +761,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,7 +798,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124571918</v>
+        <v>124572068</v>
       </c>
       <c r="B3" t="n">
         <v>56722</v>
@@ -833,10 +846,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>735703</v>
+        <v>735946</v>
       </c>
       <c r="R3" t="n">
-        <v>7094102</v>
+        <v>7094100</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124571954</v>
+        <v>124571938</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>56722</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,37 +920,33 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -947,10 +956,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>735788</v>
+        <v>735748</v>
       </c>
       <c r="R4" t="n">
-        <v>7094109</v>
+        <v>7094125</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124571976</v>
+        <v>124571960</v>
       </c>
       <c r="B5" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,25 +1030,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1047,7 +1056,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1057,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>735843</v>
+        <v>735822</v>
       </c>
       <c r="R5" t="n">
-        <v>7093984</v>
+        <v>7094149</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,7 +1128,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124572176</v>
+        <v>124571973</v>
       </c>
       <c r="B6" t="n">
         <v>56722</v>
@@ -1152,20 +1161,12 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>övernattning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1175,10 +1176,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>735831</v>
+        <v>735833</v>
       </c>
       <c r="R6" t="n">
-        <v>7094139</v>
+        <v>7094015</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,17 +1206,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,7 +1238,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124571916</v>
+        <v>124571896</v>
       </c>
       <c r="B7" t="n">
         <v>56722</v>
@@ -1290,10 +1286,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>735671</v>
+        <v>735546</v>
       </c>
       <c r="R7" t="n">
-        <v>7094195</v>
+        <v>7094241</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1326,6 +1322,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Natträd med blindtarmstömning under.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,7 +1353,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124572066</v>
+        <v>124572050</v>
       </c>
       <c r="B8" t="n">
         <v>56722</v>
@@ -1400,10 +1401,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>735937</v>
+        <v>735918</v>
       </c>
       <c r="R8" t="n">
-        <v>7094116</v>
+        <v>7094133</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1436,11 +1437,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ett av flera natträd med nattspillning och blidntarmstömning under. Dessutom kortspillning under detta. Indikerar spelplats i lämplig biotop för spel.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,10 +1463,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124572008</v>
+        <v>124571954</v>
       </c>
       <c r="B9" t="n">
-        <v>56722</v>
+        <v>57666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1479,33 +1475,37 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1515,10 +1515,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>735894</v>
+        <v>735788</v>
       </c>
       <c r="R9" t="n">
-        <v>7093968</v>
+        <v>7094109</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1577,7 +1577,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124572161</v>
+        <v>124571918</v>
       </c>
       <c r="B10" t="n">
         <v>56722</v>
@@ -1610,20 +1610,12 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>övernattning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1633,10 +1625,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>735754</v>
+        <v>735703</v>
       </c>
       <c r="R10" t="n">
-        <v>7094207</v>
+        <v>7094102</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1663,17 +1655,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1700,7 +1687,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124571938</v>
+        <v>124571916</v>
       </c>
       <c r="B11" t="n">
         <v>56722</v>
@@ -1748,10 +1735,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>735748</v>
+        <v>735671</v>
       </c>
       <c r="R11" t="n">
-        <v>7094125</v>
+        <v>7094195</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1810,7 +1797,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124572169</v>
+        <v>124571964</v>
       </c>
       <c r="B12" t="n">
         <v>56722</v>
@@ -1843,20 +1830,12 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>övernattning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1866,10 +1845,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>735753</v>
+        <v>735877</v>
       </c>
       <c r="R12" t="n">
-        <v>7094155</v>
+        <v>7094173</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1896,17 +1875,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1933,7 +1907,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124571964</v>
+        <v>124572048</v>
       </c>
       <c r="B13" t="n">
         <v>56722</v>
@@ -1981,10 +1955,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>735877</v>
+        <v>735905</v>
       </c>
       <c r="R13" t="n">
-        <v>7094173</v>
+        <v>7094143</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2043,10 +2017,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124571960</v>
+        <v>124572008</v>
       </c>
       <c r="B14" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2055,25 +2029,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2081,7 +2055,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2091,10 +2065,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>735822</v>
+        <v>735894</v>
       </c>
       <c r="R14" t="n">
-        <v>7094149</v>
+        <v>7093968</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2153,7 +2127,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124572068</v>
+        <v>124571976</v>
       </c>
       <c r="B15" t="n">
         <v>56722</v>
@@ -2201,10 +2175,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>735946</v>
+        <v>735843</v>
       </c>
       <c r="R15" t="n">
-        <v>7094100</v>
+        <v>7093984</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2263,7 +2237,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124571896</v>
+        <v>124572088</v>
       </c>
       <c r="B16" t="n">
         <v>56722</v>
@@ -2311,10 +2285,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>735546</v>
+        <v>735949</v>
       </c>
       <c r="R16" t="n">
-        <v>7094241</v>
+        <v>7094084</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2347,11 +2321,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Natträd med blindtarmstömning under.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2378,7 +2347,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124572088</v>
+        <v>124572176</v>
       </c>
       <c r="B17" t="n">
         <v>56722</v>
@@ -2411,12 +2380,20 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>övernattning</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2426,10 +2403,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>735949</v>
+        <v>735831</v>
       </c>
       <c r="R17" t="n">
-        <v>7094084</v>
+        <v>7094139</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2456,12 +2433,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2488,7 +2470,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124572050</v>
+        <v>124572169</v>
       </c>
       <c r="B18" t="n">
         <v>56722</v>
@@ -2521,12 +2503,20 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>övernattning</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2536,10 +2526,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>735918</v>
+        <v>735753</v>
       </c>
       <c r="R18" t="n">
-        <v>7094133</v>
+        <v>7094155</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2566,12 +2556,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2598,7 +2593,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124571973</v>
+        <v>124572066</v>
       </c>
       <c r="B19" t="n">
         <v>56722</v>
@@ -2646,10 +2641,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>735833</v>
+        <v>735937</v>
       </c>
       <c r="R19" t="n">
-        <v>7094015</v>
+        <v>7094116</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2682,6 +2677,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ett av flera natträd med nattspillning och blidntarmstömning under. Dessutom kortspillning under detta. Indikerar spelplats i lämplig biotop för spel.</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 4450-2025 artfynd.xlsx
+++ b/artfynd/A 4450-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124572068</v>
+        <v>124571896</v>
       </c>
       <c r="B3" t="n">
         <v>56722</v>
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>735946</v>
+        <v>735546</v>
       </c>
       <c r="R3" t="n">
-        <v>7094100</v>
+        <v>7094241</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,6 +882,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Natträd med blindtarmstömning under.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,7 +913,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124571938</v>
+        <v>124572066</v>
       </c>
       <c r="B4" t="n">
         <v>56722</v>
@@ -956,10 +961,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>735748</v>
+        <v>735937</v>
       </c>
       <c r="R4" t="n">
-        <v>7094125</v>
+        <v>7094116</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,6 +997,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ett av flera natträd med nattspillning och blidntarmstömning under. Dessutom kortspillning under detta. Indikerar spelplats i lämplig biotop för spel.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,10 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124571960</v>
+        <v>124571973</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,25 +1040,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,7 +1066,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1066,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>735822</v>
+        <v>735833</v>
       </c>
       <c r="R5" t="n">
-        <v>7094149</v>
+        <v>7094015</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1128,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124571973</v>
+        <v>124571954</v>
       </c>
       <c r="B6" t="n">
-        <v>56722</v>
+        <v>57666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,33 +1150,37 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1176,10 +1190,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>735833</v>
+        <v>735788</v>
       </c>
       <c r="R6" t="n">
-        <v>7094015</v>
+        <v>7094109</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1238,7 +1252,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124571896</v>
+        <v>124572169</v>
       </c>
       <c r="B7" t="n">
         <v>56722</v>
@@ -1271,12 +1285,20 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>övernattning</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1286,10 +1308,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>735546</v>
+        <v>735753</v>
       </c>
       <c r="R7" t="n">
-        <v>7094241</v>
+        <v>7094155</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,17 +1338,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Natträd med blindtarmstömning under.</t>
+          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1353,7 +1375,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124572050</v>
+        <v>124572068</v>
       </c>
       <c r="B8" t="n">
         <v>56722</v>
@@ -1401,10 +1423,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>735918</v>
+        <v>735946</v>
       </c>
       <c r="R8" t="n">
-        <v>7094133</v>
+        <v>7094100</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1463,10 +1485,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124571954</v>
+        <v>124572088</v>
       </c>
       <c r="B9" t="n">
-        <v>57666</v>
+        <v>56722</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,37 +1497,33 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1515,10 +1533,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>735788</v>
+        <v>735949</v>
       </c>
       <c r="R9" t="n">
-        <v>7094109</v>
+        <v>7094084</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1577,7 +1595,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124571918</v>
+        <v>124572176</v>
       </c>
       <c r="B10" t="n">
         <v>56722</v>
@@ -1610,12 +1628,20 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>övernattning</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1625,10 +1651,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>735703</v>
+        <v>735831</v>
       </c>
       <c r="R10" t="n">
-        <v>7094102</v>
+        <v>7094139</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1655,12 +1681,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1687,7 +1718,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124571916</v>
+        <v>124572048</v>
       </c>
       <c r="B11" t="n">
         <v>56722</v>
@@ -1735,10 +1766,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>735671</v>
+        <v>735905</v>
       </c>
       <c r="R11" t="n">
-        <v>7094195</v>
+        <v>7094143</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1797,10 +1828,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124571964</v>
+        <v>124571960</v>
       </c>
       <c r="B12" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1809,25 +1840,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,7 +1866,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1845,10 +1876,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>735877</v>
+        <v>735822</v>
       </c>
       <c r="R12" t="n">
-        <v>7094173</v>
+        <v>7094149</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,7 +1938,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124572048</v>
+        <v>124571976</v>
       </c>
       <c r="B13" t="n">
         <v>56722</v>
@@ -1955,10 +1986,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>735905</v>
+        <v>735843</v>
       </c>
       <c r="R13" t="n">
-        <v>7094143</v>
+        <v>7093984</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2017,7 +2048,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124572008</v>
+        <v>124571964</v>
       </c>
       <c r="B14" t="n">
         <v>56722</v>
@@ -2065,10 +2096,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>735894</v>
+        <v>735877</v>
       </c>
       <c r="R14" t="n">
-        <v>7093968</v>
+        <v>7094173</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2127,7 +2158,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124571976</v>
+        <v>124571916</v>
       </c>
       <c r="B15" t="n">
         <v>56722</v>
@@ -2175,10 +2206,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>735843</v>
+        <v>735671</v>
       </c>
       <c r="R15" t="n">
-        <v>7093984</v>
+        <v>7094195</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2237,7 +2268,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124572088</v>
+        <v>124571918</v>
       </c>
       <c r="B16" t="n">
         <v>56722</v>
@@ -2285,10 +2316,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>735949</v>
+        <v>735703</v>
       </c>
       <c r="R16" t="n">
-        <v>7094084</v>
+        <v>7094102</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2347,7 +2378,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124572176</v>
+        <v>124572050</v>
       </c>
       <c r="B17" t="n">
         <v>56722</v>
@@ -2380,20 +2411,12 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>övernattning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2403,10 +2426,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>735831</v>
+        <v>735918</v>
       </c>
       <c r="R17" t="n">
-        <v>7094139</v>
+        <v>7094133</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2433,17 +2456,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2470,7 +2488,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124572169</v>
+        <v>124572008</v>
       </c>
       <c r="B18" t="n">
         <v>56722</v>
@@ -2503,20 +2521,12 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>övernattning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2526,10 +2536,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>735753</v>
+        <v>735894</v>
       </c>
       <c r="R18" t="n">
-        <v>7094155</v>
+        <v>7093968</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2556,17 +2566,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2593,7 +2598,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124572066</v>
+        <v>124571938</v>
       </c>
       <c r="B19" t="n">
         <v>56722</v>
@@ -2641,10 +2646,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>735937</v>
+        <v>735748</v>
       </c>
       <c r="R19" t="n">
-        <v>7094116</v>
+        <v>7094125</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2677,11 +2682,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ett av flera natträd med nattspillning och blidntarmstömning under. Dessutom kortspillning under detta. Indikerar spelplats i lämplig biotop för spel.</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 4450-2025 artfynd.xlsx
+++ b/artfynd/A 4450-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124572161</v>
+        <v>124571896</v>
       </c>
       <c r="B2" t="n">
         <v>56722</v>
@@ -708,20 +708,12 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>övernattning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -731,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>735754</v>
+        <v>735546</v>
       </c>
       <c r="R2" t="n">
-        <v>7094207</v>
+        <v>7094241</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,17 +753,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
+          <t>Natträd med blindtarmstömning under.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -798,7 +790,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124571896</v>
+        <v>124572066</v>
       </c>
       <c r="B3" t="n">
         <v>56722</v>
@@ -846,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>735546</v>
+        <v>735937</v>
       </c>
       <c r="R3" t="n">
-        <v>7094241</v>
+        <v>7094116</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,7 +878,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Natträd med blindtarmstömning under.</t>
+          <t>Ett av flera natträd med nattspillning och blidntarmstömning under. Dessutom kortspillning under detta. Indikerar spelplats i lämplig biotop för spel.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,7 +905,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124572066</v>
+        <v>124572048</v>
       </c>
       <c r="B4" t="n">
         <v>56722</v>
@@ -961,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>735937</v>
+        <v>735905</v>
       </c>
       <c r="R4" t="n">
-        <v>7094116</v>
+        <v>7094143</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -997,11 +989,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ett av flera natträd med nattspillning och blidntarmstömning under. Dessutom kortspillning under detta. Indikerar spelplats i lämplig biotop för spel.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,7 +1015,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124571973</v>
+        <v>124572176</v>
       </c>
       <c r="B5" t="n">
         <v>56722</v>
@@ -1061,12 +1048,20 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>övernattning</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1076,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>735833</v>
+        <v>735831</v>
       </c>
       <c r="R5" t="n">
-        <v>7094015</v>
+        <v>7094139</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,12 +1101,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124571954</v>
+        <v>124572068</v>
       </c>
       <c r="B6" t="n">
-        <v>57666</v>
+        <v>56722</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,37 +1150,33 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1190,10 +1186,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>735788</v>
+        <v>735946</v>
       </c>
       <c r="R6" t="n">
-        <v>7094109</v>
+        <v>7094100</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1252,7 +1248,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124572169</v>
+        <v>124571916</v>
       </c>
       <c r="B7" t="n">
         <v>56722</v>
@@ -1285,20 +1281,12 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>övernattning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1308,10 +1296,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>735753</v>
+        <v>735671</v>
       </c>
       <c r="R7" t="n">
-        <v>7094155</v>
+        <v>7094195</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1338,17 +1326,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,7 +1358,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124572068</v>
+        <v>124571973</v>
       </c>
       <c r="B8" t="n">
         <v>56722</v>
@@ -1423,10 +1406,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>735946</v>
+        <v>735833</v>
       </c>
       <c r="R8" t="n">
-        <v>7094100</v>
+        <v>7094015</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1485,7 +1468,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124572088</v>
+        <v>124571976</v>
       </c>
       <c r="B9" t="n">
         <v>56722</v>
@@ -1533,10 +1516,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>735949</v>
+        <v>735843</v>
       </c>
       <c r="R9" t="n">
-        <v>7094084</v>
+        <v>7093984</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1595,7 +1578,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124572176</v>
+        <v>124571964</v>
       </c>
       <c r="B10" t="n">
         <v>56722</v>
@@ -1628,20 +1611,12 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>övernattning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1651,10 +1626,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>735831</v>
+        <v>735877</v>
       </c>
       <c r="R10" t="n">
-        <v>7094139</v>
+        <v>7094173</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1681,17 +1656,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1718,7 +1688,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124572048</v>
+        <v>124571918</v>
       </c>
       <c r="B11" t="n">
         <v>56722</v>
@@ -1766,10 +1736,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>735905</v>
+        <v>735703</v>
       </c>
       <c r="R11" t="n">
-        <v>7094143</v>
+        <v>7094102</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1828,10 +1798,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124571960</v>
+        <v>124572008</v>
       </c>
       <c r="B12" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1840,25 +1810,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1866,7 +1836,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1876,10 +1846,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>735822</v>
+        <v>735894</v>
       </c>
       <c r="R12" t="n">
-        <v>7094149</v>
+        <v>7093968</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1938,7 +1908,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124571976</v>
+        <v>124572169</v>
       </c>
       <c r="B13" t="n">
         <v>56722</v>
@@ -1971,12 +1941,20 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>övernattning</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1986,10 +1964,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>735843</v>
+        <v>735753</v>
       </c>
       <c r="R13" t="n">
-        <v>7093984</v>
+        <v>7094155</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2016,12 +1994,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2048,7 +2031,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124571964</v>
+        <v>124571938</v>
       </c>
       <c r="B14" t="n">
         <v>56722</v>
@@ -2096,10 +2079,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>735877</v>
+        <v>735748</v>
       </c>
       <c r="R14" t="n">
-        <v>7094173</v>
+        <v>7094125</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2158,7 +2141,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124571916</v>
+        <v>124572088</v>
       </c>
       <c r="B15" t="n">
         <v>56722</v>
@@ -2206,10 +2189,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>735671</v>
+        <v>735949</v>
       </c>
       <c r="R15" t="n">
-        <v>7094195</v>
+        <v>7094084</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2268,7 +2251,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124571918</v>
+        <v>124572050</v>
       </c>
       <c r="B16" t="n">
         <v>56722</v>
@@ -2316,10 +2299,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>735703</v>
+        <v>735918</v>
       </c>
       <c r="R16" t="n">
-        <v>7094102</v>
+        <v>7094133</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2378,10 +2361,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124572050</v>
+        <v>124571960</v>
       </c>
       <c r="B17" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2390,25 +2373,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2416,7 +2399,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2426,10 +2409,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>735918</v>
+        <v>735822</v>
       </c>
       <c r="R17" t="n">
-        <v>7094133</v>
+        <v>7094149</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2488,7 +2471,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124572008</v>
+        <v>124572161</v>
       </c>
       <c r="B18" t="n">
         <v>56722</v>
@@ -2521,12 +2504,20 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>övernattning</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2536,10 +2527,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>735894</v>
+        <v>735754</v>
       </c>
       <c r="R18" t="n">
-        <v>7093968</v>
+        <v>7094207</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2566,12 +2557,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2598,10 +2594,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124571938</v>
+        <v>124571954</v>
       </c>
       <c r="B19" t="n">
-        <v>56722</v>
+        <v>57666</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2610,33 +2606,37 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2646,10 +2646,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>735748</v>
+        <v>735788</v>
       </c>
       <c r="R19" t="n">
-        <v>7094125</v>
+        <v>7094109</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 4450-2025 artfynd.xlsx
+++ b/artfynd/A 4450-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124571896</v>
+        <v>124571954</v>
       </c>
       <c r="B2" t="n">
-        <v>56722</v>
+        <v>57666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,33 +687,37 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -723,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>735546</v>
+        <v>735788</v>
       </c>
       <c r="R2" t="n">
-        <v>7094241</v>
+        <v>7094109</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,11 +763,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Natträd med blindtarmstömning under.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,7 +789,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124572066</v>
+        <v>124571938</v>
       </c>
       <c r="B3" t="n">
         <v>56722</v>
@@ -838,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>735937</v>
+        <v>735748</v>
       </c>
       <c r="R3" t="n">
-        <v>7094116</v>
+        <v>7094125</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,11 +873,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ett av flera natträd med nattspillning och blidntarmstömning under. Dessutom kortspillning under detta. Indikerar spelplats i lämplig biotop för spel.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124572048</v>
+        <v>124571896</v>
       </c>
       <c r="B4" t="n">
         <v>56722</v>
@@ -953,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>735905</v>
+        <v>735546</v>
       </c>
       <c r="R4" t="n">
-        <v>7094143</v>
+        <v>7094241</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,6 +983,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Natträd med blindtarmstömning under.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,7 +1014,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124572176</v>
+        <v>124571964</v>
       </c>
       <c r="B5" t="n">
         <v>56722</v>
@@ -1048,20 +1047,12 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>övernattning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1071,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>735831</v>
+        <v>735877</v>
       </c>
       <c r="R5" t="n">
-        <v>7094139</v>
+        <v>7094173</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,17 +1092,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,7 +1124,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124572068</v>
+        <v>124572050</v>
       </c>
       <c r="B6" t="n">
         <v>56722</v>
@@ -1186,10 +1172,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>735946</v>
+        <v>735918</v>
       </c>
       <c r="R6" t="n">
-        <v>7094100</v>
+        <v>7094133</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1248,7 +1234,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124571916</v>
+        <v>124571918</v>
       </c>
       <c r="B7" t="n">
         <v>56722</v>
@@ -1296,10 +1282,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>735671</v>
+        <v>735703</v>
       </c>
       <c r="R7" t="n">
-        <v>7094195</v>
+        <v>7094102</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1358,7 +1344,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124571973</v>
+        <v>124572068</v>
       </c>
       <c r="B8" t="n">
         <v>56722</v>
@@ -1406,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>735833</v>
+        <v>735946</v>
       </c>
       <c r="R8" t="n">
-        <v>7094015</v>
+        <v>7094100</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1468,7 +1454,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124571976</v>
+        <v>124572048</v>
       </c>
       <c r="B9" t="n">
         <v>56722</v>
@@ -1516,10 +1502,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>735843</v>
+        <v>735905</v>
       </c>
       <c r="R9" t="n">
-        <v>7093984</v>
+        <v>7094143</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1578,7 +1564,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124571964</v>
+        <v>124572176</v>
       </c>
       <c r="B10" t="n">
         <v>56722</v>
@@ -1611,12 +1597,20 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>övernattning</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1626,10 +1620,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>735877</v>
+        <v>735831</v>
       </c>
       <c r="R10" t="n">
-        <v>7094173</v>
+        <v>7094139</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1656,12 +1650,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,7 +1687,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124571918</v>
+        <v>124572088</v>
       </c>
       <c r="B11" t="n">
         <v>56722</v>
@@ -1736,10 +1735,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>735703</v>
+        <v>735949</v>
       </c>
       <c r="R11" t="n">
-        <v>7094102</v>
+        <v>7094084</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1798,7 +1797,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124572008</v>
+        <v>124572169</v>
       </c>
       <c r="B12" t="n">
         <v>56722</v>
@@ -1831,12 +1830,20 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>övernattning</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1846,10 +1853,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>735894</v>
+        <v>735753</v>
       </c>
       <c r="R12" t="n">
-        <v>7093968</v>
+        <v>7094155</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1876,12 +1883,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1908,7 +1920,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124572169</v>
+        <v>124572066</v>
       </c>
       <c r="B13" t="n">
         <v>56722</v>
@@ -1941,20 +1953,12 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>övernattning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1964,10 +1968,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>735753</v>
+        <v>735937</v>
       </c>
       <c r="R13" t="n">
-        <v>7094155</v>
+        <v>7094116</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1994,17 +1998,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
+          <t>Ett av flera natträd med nattspillning och blidntarmstömning under. Dessutom kortspillning under detta. Indikerar spelplats i lämplig biotop för spel.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2031,10 +2035,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124571938</v>
+        <v>124571960</v>
       </c>
       <c r="B14" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2043,25 +2047,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2069,7 +2073,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2079,10 +2083,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>735748</v>
+        <v>735822</v>
       </c>
       <c r="R14" t="n">
-        <v>7094125</v>
+        <v>7094149</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2141,7 +2145,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124572088</v>
+        <v>124572008</v>
       </c>
       <c r="B15" t="n">
         <v>56722</v>
@@ -2189,10 +2193,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>735949</v>
+        <v>735894</v>
       </c>
       <c r="R15" t="n">
-        <v>7094084</v>
+        <v>7093968</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2251,7 +2255,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124572050</v>
+        <v>124571973</v>
       </c>
       <c r="B16" t="n">
         <v>56722</v>
@@ -2299,10 +2303,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>735918</v>
+        <v>735833</v>
       </c>
       <c r="R16" t="n">
-        <v>7094133</v>
+        <v>7094015</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2361,10 +2365,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124571960</v>
+        <v>124571976</v>
       </c>
       <c r="B17" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2373,25 +2377,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2399,7 +2403,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2409,10 +2413,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>735822</v>
+        <v>735843</v>
       </c>
       <c r="R17" t="n">
-        <v>7094149</v>
+        <v>7093984</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2594,10 +2598,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124571954</v>
+        <v>124571916</v>
       </c>
       <c r="B19" t="n">
-        <v>57666</v>
+        <v>56722</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2606,37 +2610,33 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2646,10 +2646,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>735788</v>
+        <v>735671</v>
       </c>
       <c r="R19" t="n">
-        <v>7094109</v>
+        <v>7094195</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 4450-2025 artfynd.xlsx
+++ b/artfynd/A 4450-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124571954</v>
+        <v>124572050</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
+        <v>56722</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,37 +687,33 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>735788</v>
+        <v>735918</v>
       </c>
       <c r="R2" t="n">
-        <v>7094109</v>
+        <v>7094133</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124571938</v>
+        <v>124571976</v>
       </c>
       <c r="B3" t="n">
         <v>56722</v>
@@ -837,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>735748</v>
+        <v>735843</v>
       </c>
       <c r="R3" t="n">
-        <v>7094125</v>
+        <v>7093984</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -899,7 +895,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124571896</v>
+        <v>124571964</v>
       </c>
       <c r="B4" t="n">
         <v>56722</v>
@@ -947,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>735546</v>
+        <v>735877</v>
       </c>
       <c r="R4" t="n">
-        <v>7094241</v>
+        <v>7094173</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,11 +979,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Natträd med blindtarmstömning under.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,7 +1005,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124571964</v>
+        <v>124571896</v>
       </c>
       <c r="B5" t="n">
         <v>56722</v>
@@ -1062,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>735877</v>
+        <v>735546</v>
       </c>
       <c r="R5" t="n">
-        <v>7094173</v>
+        <v>7094241</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,6 +1089,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Natträd med blindtarmstömning under.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,7 +1120,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124572050</v>
+        <v>124572088</v>
       </c>
       <c r="B6" t="n">
         <v>56722</v>
@@ -1172,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>735918</v>
+        <v>735949</v>
       </c>
       <c r="R6" t="n">
-        <v>7094133</v>
+        <v>7094084</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1234,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124571918</v>
+        <v>124571916</v>
       </c>
       <c r="B7" t="n">
         <v>56722</v>
@@ -1282,10 +1278,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>735703</v>
+        <v>735671</v>
       </c>
       <c r="R7" t="n">
-        <v>7094102</v>
+        <v>7094195</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,10 +1340,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124572068</v>
+        <v>124571960</v>
       </c>
       <c r="B8" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1356,25 +1352,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1382,7 +1378,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1392,10 +1388,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>735946</v>
+        <v>735822</v>
       </c>
       <c r="R8" t="n">
-        <v>7094100</v>
+        <v>7094149</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1564,7 +1560,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124572176</v>
+        <v>124572169</v>
       </c>
       <c r="B10" t="n">
         <v>56722</v>
@@ -1620,10 +1616,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>735831</v>
+        <v>735753</v>
       </c>
       <c r="R10" t="n">
-        <v>7094139</v>
+        <v>7094155</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1687,7 +1683,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124572088</v>
+        <v>124571973</v>
       </c>
       <c r="B11" t="n">
         <v>56722</v>
@@ -1735,10 +1731,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>735949</v>
+        <v>735833</v>
       </c>
       <c r="R11" t="n">
-        <v>7094084</v>
+        <v>7094015</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1797,10 +1793,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124572169</v>
+        <v>124571954</v>
       </c>
       <c r="B12" t="n">
-        <v>56722</v>
+        <v>57666</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1809,25 +1805,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1836,14 +1832,10 @@
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>övernattning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1853,10 +1845,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>735753</v>
+        <v>735788</v>
       </c>
       <c r="R12" t="n">
-        <v>7094155</v>
+        <v>7094109</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1883,17 +1875,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1920,7 +1907,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124572066</v>
+        <v>124572068</v>
       </c>
       <c r="B13" t="n">
         <v>56722</v>
@@ -1968,10 +1955,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>735937</v>
+        <v>735946</v>
       </c>
       <c r="R13" t="n">
-        <v>7094116</v>
+        <v>7094100</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2004,11 +1991,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ett av flera natträd med nattspillning och blidntarmstömning under. Dessutom kortspillning under detta. Indikerar spelplats i lämplig biotop för spel.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2035,10 +2017,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124571960</v>
+        <v>124571938</v>
       </c>
       <c r="B14" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2047,25 +2029,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2073,7 +2055,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2083,10 +2065,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>735822</v>
+        <v>735748</v>
       </c>
       <c r="R14" t="n">
-        <v>7094149</v>
+        <v>7094125</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2145,7 +2127,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124572008</v>
+        <v>124572161</v>
       </c>
       <c r="B15" t="n">
         <v>56722</v>
@@ -2178,12 +2160,20 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>övernattning</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2193,10 +2183,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>735894</v>
+        <v>735754</v>
       </c>
       <c r="R15" t="n">
-        <v>7093968</v>
+        <v>7094207</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2223,12 +2213,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2255,7 +2250,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124571973</v>
+        <v>124572066</v>
       </c>
       <c r="B16" t="n">
         <v>56722</v>
@@ -2303,10 +2298,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>735833</v>
+        <v>735937</v>
       </c>
       <c r="R16" t="n">
-        <v>7094015</v>
+        <v>7094116</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2339,6 +2334,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ett av flera natträd med nattspillning och blidntarmstömning under. Dessutom kortspillning under detta. Indikerar spelplats i lämplig biotop för spel.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2365,7 +2365,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124571976</v>
+        <v>124572008</v>
       </c>
       <c r="B17" t="n">
         <v>56722</v>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>735843</v>
+        <v>735894</v>
       </c>
       <c r="R17" t="n">
-        <v>7093984</v>
+        <v>7093968</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2475,7 +2475,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124572161</v>
+        <v>124572176</v>
       </c>
       <c r="B18" t="n">
         <v>56722</v>
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>735754</v>
+        <v>735831</v>
       </c>
       <c r="R18" t="n">
-        <v>7094207</v>
+        <v>7094139</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2598,7 +2598,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124571916</v>
+        <v>124571918</v>
       </c>
       <c r="B19" t="n">
         <v>56722</v>
@@ -2646,10 +2646,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>735671</v>
+        <v>735703</v>
       </c>
       <c r="R19" t="n">
-        <v>7094195</v>
+        <v>7094102</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 4450-2025 artfynd.xlsx
+++ b/artfynd/A 4450-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124572050</v>
+        <v>124571954</v>
       </c>
       <c r="B2" t="n">
-        <v>56722</v>
+        <v>57666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,33 +687,37 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -723,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>735918</v>
+        <v>735788</v>
       </c>
       <c r="R2" t="n">
-        <v>7094133</v>
+        <v>7094109</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,7 +789,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124571976</v>
+        <v>124572068</v>
       </c>
       <c r="B3" t="n">
         <v>56722</v>
@@ -833,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>735843</v>
+        <v>735946</v>
       </c>
       <c r="R3" t="n">
-        <v>7093984</v>
+        <v>7094100</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124571964</v>
+        <v>124572048</v>
       </c>
       <c r="B4" t="n">
         <v>56722</v>
@@ -943,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>735877</v>
+        <v>735905</v>
       </c>
       <c r="R4" t="n">
-        <v>7094173</v>
+        <v>7094143</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,7 +1009,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124571896</v>
+        <v>124571976</v>
       </c>
       <c r="B5" t="n">
         <v>56722</v>
@@ -1053,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>735546</v>
+        <v>735843</v>
       </c>
       <c r="R5" t="n">
-        <v>7094241</v>
+        <v>7093984</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,11 +1093,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Natträd med blindtarmstömning under.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124572088</v>
+        <v>124572008</v>
       </c>
       <c r="B6" t="n">
         <v>56722</v>
@@ -1168,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>735949</v>
+        <v>735894</v>
       </c>
       <c r="R6" t="n">
-        <v>7094084</v>
+        <v>7093968</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,7 +1229,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124571916</v>
+        <v>124572066</v>
       </c>
       <c r="B7" t="n">
         <v>56722</v>
@@ -1278,10 +1277,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>735671</v>
+        <v>735937</v>
       </c>
       <c r="R7" t="n">
-        <v>7094195</v>
+        <v>7094116</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,6 +1313,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ett av flera natträd med nattspillning och blidntarmstömning under. Dessutom kortspillning under detta. Indikerar spelplats i lämplig biotop för spel.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1340,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124571960</v>
+        <v>124571916</v>
       </c>
       <c r="B8" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1352,25 +1356,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1378,7 +1382,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1388,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>735822</v>
+        <v>735671</v>
       </c>
       <c r="R8" t="n">
-        <v>7094149</v>
+        <v>7094195</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1450,7 +1454,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124572048</v>
+        <v>124572169</v>
       </c>
       <c r="B9" t="n">
         <v>56722</v>
@@ -1483,12 +1487,20 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>övernattning</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1498,10 +1510,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>735905</v>
+        <v>735753</v>
       </c>
       <c r="R9" t="n">
-        <v>7094143</v>
+        <v>7094155</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1528,12 +1540,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1560,7 +1577,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124572169</v>
+        <v>124571973</v>
       </c>
       <c r="B10" t="n">
         <v>56722</v>
@@ -1593,20 +1610,12 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>övernattning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1616,10 +1625,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>735753</v>
+        <v>735833</v>
       </c>
       <c r="R10" t="n">
-        <v>7094155</v>
+        <v>7094015</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1646,17 +1655,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,7 +1687,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124571973</v>
+        <v>124572176</v>
       </c>
       <c r="B11" t="n">
         <v>56722</v>
@@ -1716,12 +1720,20 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>övernattning</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1731,10 +1743,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>735833</v>
+        <v>735831</v>
       </c>
       <c r="R11" t="n">
-        <v>7094015</v>
+        <v>7094139</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1761,12 +1773,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1793,10 +1810,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124571954</v>
+        <v>124572088</v>
       </c>
       <c r="B12" t="n">
-        <v>57666</v>
+        <v>56722</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1805,37 +1822,33 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1845,10 +1858,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>735788</v>
+        <v>735949</v>
       </c>
       <c r="R12" t="n">
-        <v>7094109</v>
+        <v>7094084</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,7 +1920,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124572068</v>
+        <v>124571918</v>
       </c>
       <c r="B13" t="n">
         <v>56722</v>
@@ -1955,10 +1968,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>735946</v>
+        <v>735703</v>
       </c>
       <c r="R13" t="n">
-        <v>7094100</v>
+        <v>7094102</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2017,7 +2030,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124571938</v>
+        <v>124571896</v>
       </c>
       <c r="B14" t="n">
         <v>56722</v>
@@ -2065,10 +2078,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>735748</v>
+        <v>735546</v>
       </c>
       <c r="R14" t="n">
-        <v>7094125</v>
+        <v>7094241</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2101,6 +2114,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Natträd med blindtarmstömning under.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2127,7 +2145,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124572161</v>
+        <v>124571938</v>
       </c>
       <c r="B15" t="n">
         <v>56722</v>
@@ -2160,20 +2178,12 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>övernattning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2183,10 +2193,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>735754</v>
+        <v>735748</v>
       </c>
       <c r="R15" t="n">
-        <v>7094207</v>
+        <v>7094125</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2213,17 +2223,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2250,7 +2255,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124572066</v>
+        <v>124572050</v>
       </c>
       <c r="B16" t="n">
         <v>56722</v>
@@ -2298,10 +2303,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>735937</v>
+        <v>735918</v>
       </c>
       <c r="R16" t="n">
-        <v>7094116</v>
+        <v>7094133</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2334,11 +2339,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ett av flera natträd med nattspillning och blidntarmstömning under. Dessutom kortspillning under detta. Indikerar spelplats i lämplig biotop för spel.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2365,7 +2365,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124572008</v>
+        <v>124571964</v>
       </c>
       <c r="B17" t="n">
         <v>56722</v>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>735894</v>
+        <v>735877</v>
       </c>
       <c r="R17" t="n">
-        <v>7093968</v>
+        <v>7094173</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2475,7 +2475,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124572176</v>
+        <v>124572161</v>
       </c>
       <c r="B18" t="n">
         <v>56722</v>
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>735831</v>
+        <v>735754</v>
       </c>
       <c r="R18" t="n">
-        <v>7094139</v>
+        <v>7094207</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2598,10 +2598,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124571918</v>
+        <v>124571960</v>
       </c>
       <c r="B19" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2610,25 +2610,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2636,7 +2636,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2646,10 +2646,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>735703</v>
+        <v>735822</v>
       </c>
       <c r="R19" t="n">
-        <v>7094102</v>
+        <v>7094149</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 4450-2025 artfynd.xlsx
+++ b/artfynd/A 4450-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124571954</v>
+        <v>124572050</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
+        <v>56722</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,37 +687,33 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>735788</v>
+        <v>735918</v>
       </c>
       <c r="R2" t="n">
-        <v>7094109</v>
+        <v>7094133</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -899,7 +895,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124572048</v>
+        <v>124572088</v>
       </c>
       <c r="B4" t="n">
         <v>56722</v>
@@ -947,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>735905</v>
+        <v>735949</v>
       </c>
       <c r="R4" t="n">
-        <v>7094143</v>
+        <v>7094084</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,7 +1005,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124571976</v>
+        <v>124572161</v>
       </c>
       <c r="B5" t="n">
         <v>56722</v>
@@ -1042,12 +1038,20 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>övernattning</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1057,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>735843</v>
+        <v>735754</v>
       </c>
       <c r="R5" t="n">
-        <v>7093984</v>
+        <v>7094207</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1087,12 +1091,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124572008</v>
+        <v>124571960</v>
       </c>
       <c r="B6" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,25 +1140,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1157,7 +1166,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1167,10 +1176,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>735894</v>
+        <v>735822</v>
       </c>
       <c r="R6" t="n">
-        <v>7093968</v>
+        <v>7094149</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1229,7 +1238,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124572066</v>
+        <v>124572169</v>
       </c>
       <c r="B7" t="n">
         <v>56722</v>
@@ -1262,12 +1271,20 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>övernattning</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1277,10 +1294,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>735937</v>
+        <v>735753</v>
       </c>
       <c r="R7" t="n">
-        <v>7094116</v>
+        <v>7094155</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,17 +1324,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ett av flera natträd med nattspillning och blidntarmstömning under. Dessutom kortspillning under detta. Indikerar spelplats i lämplig biotop för spel.</t>
+          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1344,7 +1361,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124571916</v>
+        <v>124571964</v>
       </c>
       <c r="B8" t="n">
         <v>56722</v>
@@ -1392,10 +1409,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>735671</v>
+        <v>735877</v>
       </c>
       <c r="R8" t="n">
-        <v>7094195</v>
+        <v>7094173</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1454,7 +1471,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124572169</v>
+        <v>124571938</v>
       </c>
       <c r="B9" t="n">
         <v>56722</v>
@@ -1487,20 +1504,12 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>övernattning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1510,10 +1519,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>735753</v>
+        <v>735748</v>
       </c>
       <c r="R9" t="n">
-        <v>7094155</v>
+        <v>7094125</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1540,17 +1549,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1687,7 +1691,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124572176</v>
+        <v>124572008</v>
       </c>
       <c r="B11" t="n">
         <v>56722</v>
@@ -1720,20 +1724,12 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>övernattning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1743,10 +1739,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>735831</v>
+        <v>735894</v>
       </c>
       <c r="R11" t="n">
-        <v>7094139</v>
+        <v>7093968</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1773,17 +1769,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1810,7 +1801,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124572088</v>
+        <v>124571976</v>
       </c>
       <c r="B12" t="n">
         <v>56722</v>
@@ -1858,10 +1849,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>735949</v>
+        <v>735843</v>
       </c>
       <c r="R12" t="n">
-        <v>7094084</v>
+        <v>7093984</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1920,7 +1911,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124571918</v>
+        <v>124571896</v>
       </c>
       <c r="B13" t="n">
         <v>56722</v>
@@ -1968,10 +1959,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>735703</v>
+        <v>735546</v>
       </c>
       <c r="R13" t="n">
-        <v>7094102</v>
+        <v>7094241</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2004,6 +1995,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Natträd med blindtarmstömning under.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2030,10 +2026,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124571896</v>
+        <v>124571954</v>
       </c>
       <c r="B14" t="n">
-        <v>56722</v>
+        <v>57666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2042,33 +2038,37 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2078,10 +2078,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>735546</v>
+        <v>735788</v>
       </c>
       <c r="R14" t="n">
-        <v>7094241</v>
+        <v>7094109</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2114,11 +2114,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Natträd med blindtarmstömning under.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2145,7 +2140,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124571938</v>
+        <v>124572066</v>
       </c>
       <c r="B15" t="n">
         <v>56722</v>
@@ -2193,10 +2188,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>735748</v>
+        <v>735937</v>
       </c>
       <c r="R15" t="n">
-        <v>7094125</v>
+        <v>7094116</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2229,6 +2224,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ett av flera natträd med nattspillning och blidntarmstömning under. Dessutom kortspillning under detta. Indikerar spelplats i lämplig biotop för spel.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2255,7 +2255,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124572050</v>
+        <v>124571918</v>
       </c>
       <c r="B16" t="n">
         <v>56722</v>
@@ -2303,10 +2303,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>735918</v>
+        <v>735703</v>
       </c>
       <c r="R16" t="n">
-        <v>7094133</v>
+        <v>7094102</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2365,7 +2365,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124571964</v>
+        <v>124571916</v>
       </c>
       <c r="B17" t="n">
         <v>56722</v>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>735877</v>
+        <v>735671</v>
       </c>
       <c r="R17" t="n">
-        <v>7094173</v>
+        <v>7094195</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2475,7 +2475,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124572161</v>
+        <v>124572048</v>
       </c>
       <c r="B18" t="n">
         <v>56722</v>
@@ -2508,20 +2508,12 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>övernattning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2531,10 +2523,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>735754</v>
+        <v>735905</v>
       </c>
       <c r="R18" t="n">
-        <v>7094207</v>
+        <v>7094143</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2561,17 +2553,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2598,10 +2585,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124571960</v>
+        <v>124572176</v>
       </c>
       <c r="B19" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2610,33 +2597,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>övernattning</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2646,10 +2641,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>735822</v>
+        <v>735831</v>
       </c>
       <c r="R19" t="n">
-        <v>7094149</v>
+        <v>7094139</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2676,12 +2671,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Lyfte ur natträd. Obs i speltid, lämplig biotop.</t>
         </is>
       </c>
       <c r="AD19" t="b">
